--- a/AAII_Financials/Yearly/NMRK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NMRK_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="92">
   <si>
     <t>NMRK</t>
   </si>
@@ -656,58 +656,58 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -717,39 +717,42 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2470400</v>
+      </c>
+      <c r="E8" s="3">
         <v>2705500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2906400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1905000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2218100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2047600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1596500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1350000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1200200</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -759,39 +762,42 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E9" s="3">
         <v>28500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>23800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>22600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>25000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>26200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>20800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>18000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18500</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -801,39 +807,42 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2443200</v>
+      </c>
+      <c r="E10" s="3">
         <v>2677000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2882700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1882400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2193100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2021400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1575700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1332000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1181800</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -843,9 +852,12 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,8 +874,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -903,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,33 +961,36 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E14" s="3">
         <v>14400</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>6000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>6600</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>6300</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
@@ -987,39 +1006,42 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>166200</v>
+      </c>
+      <c r="E15" s="3">
         <v>165800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>121700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>135200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>124500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>97700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>89900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>73100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>72000</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1029,9 +1051,12 @@
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,38 +1070,39 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2345200</v>
+      </c>
+      <c r="E17" s="3">
         <v>2520000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1651900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1721000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1971900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1715000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1396700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1182600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1211500</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1086,39 +1112,42 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>125200</v>
+      </c>
+      <c r="E18" s="3">
         <v>185600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1254600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>184000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>246200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>332600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>199800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>167400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-11200</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1128,9 +1157,12 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,38 +1179,39 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-21700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-31000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-33500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-37700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-32100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-50200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1900</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1188,36 +1221,39 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>269700</v>
+      </c>
+      <c r="E21" s="3">
         <v>320400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1342800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>287500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>345300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>380100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>298400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>243400</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1230,9 +1266,12 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1272,39 +1311,42 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>103500</v>
+      </c>
+      <c r="E23" s="3">
         <v>154600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1221100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>146300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>214100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>282400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>202600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>171200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9400</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1314,39 +1356,42 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>41100</v>
+      </c>
+      <c r="E24" s="3">
         <v>42100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>243000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>37000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>52400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>90500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-7200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-6600</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1356,9 +1401,12 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,39 +1446,42 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>62400</v>
+      </c>
+      <c r="E26" s="3">
         <v>112500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>978100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>109300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>161700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>191900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>209800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>167200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2700</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1440,39 +1491,42 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E27" s="3">
         <v>83300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>744500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>70300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>104400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>101600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>209200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>168400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2800</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1482,9 +1536,12 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,9 +1581,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1545,12 +1605,12 @@
       <c r="H29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J29" s="3">
         <v>-64700</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
       </c>
@@ -1566,9 +1626,12 @@
       <c r="O29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,39 +1716,42 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E32" s="3">
         <v>31000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>33500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>37700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>32100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>50200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1900</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1692,39 +1761,42 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E33" s="3">
         <v>83300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>744500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>70300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>104400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>101600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>144500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>168400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2800</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1734,9 +1806,12 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,39 +1851,42 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E35" s="3">
         <v>83300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>744500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>70300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>104400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>101600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>144500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>168400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2800</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1818,44 +1896,47 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1865,9 +1946,12 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,38 +1987,39 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>164900</v>
+      </c>
+      <c r="E41" s="3">
         <v>233000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>191300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>191400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>163600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>122500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>121000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>66600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>111400</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1943,33 +2029,36 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>100</v>
+      </c>
+      <c r="E42" s="3">
         <v>800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>524600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>33300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>36800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>48900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>57600</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1985,39 +2074,42 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>632100</v>
+      </c>
+      <c r="E43" s="3">
         <v>545700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>594900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1472800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>746200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1473000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>573100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1331800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>643600</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2027,9 +2119,12 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2069,39 +2164,42 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>709000</v>
+      </c>
+      <c r="E45" s="3">
         <v>296500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1213600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>121500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>127000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>112700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>73300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>84300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>71900</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2111,39 +2209,42 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1506100</v>
+      </c>
+      <c r="E46" s="3">
         <v>1076000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2524400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1819100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1073500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1757100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>825100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1482700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>826900</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2153,39 +2254,42 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>656100</v>
+      </c>
+      <c r="E47" s="3">
         <v>600800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>561700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>552500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>597800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>440300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>317100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>187100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>94300</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2195,39 +2299,42 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>774400</v>
+      </c>
+      <c r="E48" s="3">
         <v>794200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>742400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>286800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>299700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>78800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>64800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>56500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>25800</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2237,39 +2344,42 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1391400</v>
+      </c>
+      <c r="E49" s="3">
         <v>1355400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1283600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1099300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1016800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>962900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>895100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>783000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>684000</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2279,9 +2389,12 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,39 +2479,42 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>143600</v>
+      </c>
+      <c r="E52" s="3">
         <v>114300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>104200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>224700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>213800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>215100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>170900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>25500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>26800</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2405,9 +2524,12 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,39 +2569,42 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4471600</v>
+      </c>
+      <c r="E54" s="3">
         <v>3940800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5216200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3982400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3201600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3454200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2273000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2534700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1657900</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2489,9 +2614,12 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,38 +2655,39 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>266500</v>
+      </c>
+      <c r="E57" s="3">
         <v>208200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>223200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>97300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>189200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>113700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>79400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>57500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>48700</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2567,39 +2697,42 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>498600</v>
+      </c>
+      <c r="E58" s="3">
         <v>685200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1190700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1094500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>246400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>972400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>418100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>258000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>359600</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2609,39 +2742,42 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>724500</v>
+      </c>
+      <c r="E59" s="3">
         <v>682700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>778900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>513500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>609800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>578500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>285100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1094900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>317700</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2651,39 +2787,42 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1489600</v>
+      </c>
+      <c r="E60" s="3">
         <v>1576100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2192700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1705300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1045400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1664600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>782600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1410400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>726000</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2693,39 +2832,42 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>547300</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>545200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>680400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>589300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>537900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1083200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>300</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2735,39 +2877,42 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>839800</v>
+      </c>
+      <c r="E62" s="3">
         <v>823300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>793100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>655600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>604800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>168600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>163800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>140100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>127600</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2777,9 +2922,12 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,39 +3057,42 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3218600</v>
+      </c>
+      <c r="E66" s="3">
         <v>2759400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3938300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3327400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2601900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2886600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2012600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1552900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>857700</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2945,9 +3102,12 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,33 +3301,36 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1166700</v>
+      </c>
+      <c r="E72" s="3">
         <v>1145000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1079700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>342800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>313100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>278000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>199500</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3173,9 +3346,12 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,39 +3481,42 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1252900</v>
+      </c>
+      <c r="E76" s="3">
         <v>1181300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1277900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>655000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>599700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>567600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>260400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>981800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>800200</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3341,9 +3526,12 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,44 +3571,47 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3430,39 +3621,42 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E81" s="3">
         <v>83300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>744500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>70300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>104400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>101600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>144500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>168400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2800</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3472,9 +3666,12 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,35 +3688,36 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>166200</v>
+      </c>
+      <c r="E83" s="3">
         <v>165800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>121700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>141200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>131100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>97700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>95800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>72200</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,9 +3730,12 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,36 +3955,39 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-266000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1196300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-48700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-777700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>986800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-332400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>853600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-644200</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3784,9 +4000,12 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,35 +4022,36 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-55400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-62200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-19700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-19600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-34500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-21000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-19100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-27300</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3844,9 +4064,12 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,36 +4154,39 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-49700</v>
+      </c>
+      <c r="E94" s="3">
         <v>308600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>453100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-56800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>7700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-34400</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3970,9 +4199,12 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,29 +4221,30 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="E96" s="3">
         <v>-17900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-7600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-23200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-69200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-41800</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
@@ -4030,9 +4263,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,36 +4398,39 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>261500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1458500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-396300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>817800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-895500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>338700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-798200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>636000</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4198,9 +4443,12 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4225,11 +4473,11 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4240,36 +4488,39 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-54200</v>
+      </c>
+      <c r="E102" s="3">
         <v>46500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>8100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>36500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>34500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>14000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>55800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-42600</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4282,7 +4533,10 @@
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/NMRK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NMRK_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="92">
   <si>
     <t>NMRK</t>
   </si>
@@ -771,26 +771,26 @@
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
-        <v>27200</v>
-      </c>
-      <c r="E9" s="3">
-        <v>28500</v>
-      </c>
-      <c r="F9" s="3">
-        <v>23800</v>
-      </c>
-      <c r="G9" s="3">
-        <v>22600</v>
-      </c>
-      <c r="H9" s="3">
-        <v>25000</v>
-      </c>
-      <c r="I9" s="3">
-        <v>26200</v>
-      </c>
-      <c r="J9" s="3">
-        <v>20800</v>
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K9" s="3">
         <v>18000</v>
@@ -817,25 +817,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>2443200</v>
+        <v>2470400</v>
       </c>
       <c r="E10" s="3">
-        <v>2677000</v>
+        <v>2705500</v>
       </c>
       <c r="F10" s="3">
-        <v>2882700</v>
+        <v>2906400</v>
       </c>
       <c r="G10" s="3">
-        <v>1882400</v>
+        <v>1905000</v>
       </c>
       <c r="H10" s="3">
-        <v>2193100</v>
+        <v>2218100</v>
       </c>
       <c r="I10" s="3">
-        <v>2021400</v>
+        <v>2047600</v>
       </c>
       <c r="J10" s="3">
-        <v>1575700</v>
+        <v>1596500</v>
       </c>
       <c r="K10" s="3">
         <v>1332000</v>
@@ -880,26 +880,26 @@
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
+      <c r="D12" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H12" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I12" s="3">
+        <v>900</v>
+      </c>
+      <c r="J12" s="3">
+        <v>400</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
@@ -971,25 +971,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>7600</v>
+        <v>20400</v>
       </c>
       <c r="E14" s="3">
-        <v>14400</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
+        <v>128100</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-1227900</v>
       </c>
       <c r="G14" s="3">
-        <v>6000</v>
+        <v>-25700</v>
       </c>
       <c r="H14" s="3">
-        <v>6600</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+        <v>-69700</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-123700</v>
       </c>
       <c r="J14" s="3">
-        <v>6300</v>
+        <v>-68000</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -1016,10 +1016,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>166200</v>
+        <v>163000</v>
       </c>
       <c r="E15" s="3">
-        <v>165800</v>
+        <v>151800</v>
       </c>
       <c r="F15" s="3">
         <v>121700</v>
@@ -1028,13 +1028,13 @@
         <v>135200</v>
       </c>
       <c r="H15" s="3">
-        <v>124500</v>
+        <v>126100</v>
       </c>
       <c r="I15" s="3">
         <v>97700</v>
       </c>
       <c r="J15" s="3">
-        <v>89900</v>
+        <v>89500</v>
       </c>
       <c r="K15" s="3">
         <v>73100</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2345200</v>
+        <v>2338900</v>
       </c>
       <c r="E17" s="3">
-        <v>2520000</v>
+        <v>2394700</v>
       </c>
       <c r="F17" s="3">
-        <v>1651900</v>
+        <v>2879700</v>
       </c>
       <c r="G17" s="3">
-        <v>1721000</v>
+        <v>1735100</v>
       </c>
       <c r="H17" s="3">
-        <v>1971900</v>
+        <v>2048800</v>
       </c>
       <c r="I17" s="3">
-        <v>1715000</v>
+        <v>1841500</v>
       </c>
       <c r="J17" s="3">
-        <v>1396700</v>
+        <v>1466200</v>
       </c>
       <c r="K17" s="3">
         <v>1182600</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>125200</v>
+        <v>131400</v>
       </c>
       <c r="E18" s="3">
-        <v>185600</v>
+        <v>310800</v>
       </c>
       <c r="F18" s="3">
-        <v>1254600</v>
+        <v>26700</v>
       </c>
       <c r="G18" s="3">
-        <v>184000</v>
+        <v>169900</v>
       </c>
       <c r="H18" s="3">
-        <v>246200</v>
+        <v>169300</v>
       </c>
       <c r="I18" s="3">
-        <v>332600</v>
+        <v>206100</v>
       </c>
       <c r="J18" s="3">
-        <v>199800</v>
+        <v>130200</v>
       </c>
       <c r="K18" s="3">
         <v>167400</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-21700</v>
+        <v>-14200</v>
       </c>
       <c r="E20" s="3">
-        <v>-31000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-33500</v>
+        <v>-2800</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G20" s="3">
-        <v>-37700</v>
+        <v>11900</v>
       </c>
       <c r="H20" s="3">
-        <v>-32100</v>
+        <v>-6600</v>
       </c>
       <c r="I20" s="3">
-        <v>-50200</v>
+        <v>41900</v>
       </c>
       <c r="J20" s="3">
-        <v>2800</v>
+        <v>-1600</v>
       </c>
       <c r="K20" s="3">
         <v>3800</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>269700</v>
+        <v>308700</v>
       </c>
       <c r="E21" s="3">
-        <v>320400</v>
+        <v>465500</v>
       </c>
       <c r="F21" s="3">
-        <v>1342800</v>
+        <v>148400</v>
       </c>
       <c r="G21" s="3">
-        <v>287500</v>
+        <v>293200</v>
       </c>
       <c r="H21" s="3">
-        <v>345300</v>
+        <v>302100</v>
       </c>
       <c r="I21" s="3">
-        <v>380100</v>
+        <v>262000</v>
       </c>
       <c r="J21" s="3">
-        <v>298400</v>
+        <v>221300</v>
       </c>
       <c r="K21" s="3">
         <v>243400</v>
@@ -1276,25 +1276,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>38300</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>33700</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>35300</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>40300</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>36600</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>90500</v>
       </c>
       <c r="J24" s="3">
-        <v>-7200</v>
+        <v>57500</v>
       </c>
       <c r="K24" s="3">
         <v>4000</v>
@@ -1474,7 +1474,7 @@
         <v>191900</v>
       </c>
       <c r="J26" s="3">
-        <v>209800</v>
+        <v>145100</v>
       </c>
       <c r="K26" s="3">
         <v>167200</v>
@@ -1519,7 +1519,7 @@
         <v>101600</v>
       </c>
       <c r="J27" s="3">
-        <v>209200</v>
+        <v>144500</v>
       </c>
       <c r="K27" s="3">
         <v>168400</v>
@@ -1590,26 +1590,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-64700</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>21700</v>
+        <v>14200</v>
       </c>
       <c r="E32" s="3">
-        <v>31000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>33500</v>
+        <v>2800</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G32" s="3">
-        <v>37700</v>
+        <v>-11900</v>
       </c>
       <c r="H32" s="3">
-        <v>32100</v>
+        <v>6600</v>
       </c>
       <c r="I32" s="3">
-        <v>50200</v>
+        <v>-41900</v>
       </c>
       <c r="J32" s="3">
-        <v>-2800</v>
+        <v>1600</v>
       </c>
       <c r="K32" s="3">
         <v>-3800</v>
@@ -1777,16 +1777,16 @@
         <v>83300</v>
       </c>
       <c r="F33" s="3">
-        <v>744500</v>
+        <v>750700</v>
       </c>
       <c r="G33" s="3">
-        <v>70300</v>
+        <v>80100</v>
       </c>
       <c r="H33" s="3">
-        <v>104400</v>
+        <v>117300</v>
       </c>
       <c r="I33" s="3">
-        <v>101600</v>
+        <v>106700</v>
       </c>
       <c r="J33" s="3">
         <v>144500</v>
@@ -1867,16 +1867,16 @@
         <v>83300</v>
       </c>
       <c r="F35" s="3">
-        <v>744500</v>
+        <v>750700</v>
       </c>
       <c r="G35" s="3">
-        <v>70300</v>
+        <v>80100</v>
       </c>
       <c r="H35" s="3">
-        <v>104400</v>
+        <v>117300</v>
       </c>
       <c r="I35" s="3">
-        <v>101600</v>
+        <v>106700</v>
       </c>
       <c r="J35" s="3">
         <v>144500</v>
@@ -2093,16 +2093,16 @@
         <v>594900</v>
       </c>
       <c r="G43" s="3">
-        <v>1472800</v>
+        <v>386000</v>
       </c>
       <c r="H43" s="3">
-        <v>746200</v>
+        <v>530900</v>
       </c>
       <c r="I43" s="3">
-        <v>1473000</v>
+        <v>482100</v>
       </c>
       <c r="J43" s="3">
-        <v>573100</v>
+        <v>210500</v>
       </c>
       <c r="K43" s="3">
         <v>1331800</v>
@@ -2128,26 +2128,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>709000</v>
+        <v>34900</v>
       </c>
       <c r="E45" s="3">
-        <v>296500</v>
+        <v>37800</v>
       </c>
       <c r="F45" s="3">
-        <v>1213600</v>
+        <v>29500</v>
       </c>
       <c r="G45" s="3">
-        <v>121500</v>
+        <v>35700</v>
       </c>
       <c r="H45" s="3">
-        <v>127000</v>
+        <v>53500</v>
       </c>
       <c r="I45" s="3">
-        <v>112700</v>
+        <v>32200</v>
       </c>
       <c r="J45" s="3">
-        <v>73300</v>
+        <v>8300</v>
       </c>
       <c r="K45" s="3">
         <v>84300</v>
@@ -2264,25 +2264,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>656100</v>
+        <v>4900</v>
       </c>
       <c r="E47" s="3">
-        <v>600800</v>
+        <v>100000</v>
       </c>
       <c r="F47" s="3">
-        <v>561700</v>
+        <v>108300</v>
       </c>
       <c r="G47" s="3">
-        <v>552500</v>
+        <v>111000</v>
       </c>
       <c r="H47" s="3">
-        <v>597800</v>
+        <v>194100</v>
       </c>
       <c r="I47" s="3">
-        <v>440300</v>
+        <v>154700</v>
       </c>
       <c r="J47" s="3">
-        <v>317100</v>
+        <v>107600</v>
       </c>
       <c r="K47" s="3">
         <v>187100</v>
@@ -2363,7 +2363,7 @@
         <v>1283600</v>
       </c>
       <c r="G49" s="3">
-        <v>1099300</v>
+        <v>1099400</v>
       </c>
       <c r="H49" s="3">
         <v>1016800</v>
@@ -2489,25 +2489,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>143600</v>
+        <v>43400</v>
       </c>
       <c r="E52" s="3">
-        <v>114300</v>
+        <v>19600</v>
       </c>
       <c r="F52" s="3">
-        <v>104200</v>
+        <v>34000</v>
       </c>
       <c r="G52" s="3">
-        <v>224700</v>
+        <v>24400</v>
       </c>
       <c r="H52" s="3">
-        <v>213800</v>
+        <v>31000</v>
       </c>
       <c r="I52" s="3">
-        <v>215100</v>
+        <v>65200</v>
       </c>
       <c r="J52" s="3">
-        <v>170900</v>
+        <v>2300</v>
       </c>
       <c r="K52" s="3">
         <v>25500</v>
@@ -2588,7 +2588,7 @@
         <v>5216200</v>
       </c>
       <c r="G54" s="3">
-        <v>3982400</v>
+        <v>3982500</v>
       </c>
       <c r="H54" s="3">
         <v>3201600</v>
@@ -2674,7 +2674,7 @@
         <v>97300</v>
       </c>
       <c r="H57" s="3">
-        <v>189200</v>
+        <v>162000</v>
       </c>
       <c r="I57" s="3">
         <v>113700</v>
@@ -2707,19 +2707,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>498600</v>
+        <v>605700</v>
       </c>
       <c r="E58" s="3">
-        <v>685200</v>
+        <v>782100</v>
       </c>
       <c r="F58" s="3">
-        <v>1190700</v>
+        <v>1272700</v>
       </c>
       <c r="G58" s="3">
-        <v>1094500</v>
+        <v>1123900</v>
       </c>
       <c r="H58" s="3">
-        <v>246400</v>
+        <v>273600</v>
       </c>
       <c r="I58" s="3">
         <v>972400</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>724500</v>
+        <v>39800</v>
       </c>
       <c r="E59" s="3">
-        <v>682700</v>
+        <v>42100</v>
       </c>
       <c r="F59" s="3">
-        <v>778900</v>
+        <v>80700</v>
       </c>
       <c r="G59" s="3">
-        <v>513500</v>
+        <v>90000</v>
       </c>
       <c r="H59" s="3">
-        <v>609800</v>
+        <v>146100</v>
       </c>
       <c r="I59" s="3">
-        <v>578500</v>
+        <v>112500</v>
       </c>
       <c r="J59" s="3">
-        <v>285100</v>
+        <v>50400</v>
       </c>
       <c r="K59" s="3">
         <v>1094900</v>
@@ -2842,19 +2842,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>547300</v>
+        <v>1145300</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>627100</v>
       </c>
       <c r="F61" s="3">
-        <v>545200</v>
+        <v>1131300</v>
       </c>
       <c r="G61" s="3">
-        <v>680400</v>
+        <v>899000</v>
       </c>
       <c r="H61" s="3">
-        <v>589300</v>
+        <v>817200</v>
       </c>
       <c r="I61" s="3">
         <v>537900</v>
@@ -2887,19 +2887,19 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>839800</v>
+        <v>235400</v>
       </c>
       <c r="E62" s="3">
-        <v>823300</v>
+        <v>191200</v>
       </c>
       <c r="F62" s="3">
-        <v>793100</v>
+        <v>207000</v>
       </c>
       <c r="G62" s="3">
-        <v>655600</v>
+        <v>437000</v>
       </c>
       <c r="H62" s="3">
-        <v>604800</v>
+        <v>376800</v>
       </c>
       <c r="I62" s="3">
         <v>168600</v>
@@ -3067,25 +3067,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3218600</v>
+        <v>2876600</v>
       </c>
       <c r="E66" s="3">
-        <v>2759400</v>
+        <v>2399300</v>
       </c>
       <c r="F66" s="3">
-        <v>3938300</v>
+        <v>3531100</v>
       </c>
       <c r="G66" s="3">
-        <v>3327400</v>
+        <v>3041300</v>
       </c>
       <c r="H66" s="3">
-        <v>2601900</v>
+        <v>2239500</v>
       </c>
       <c r="I66" s="3">
-        <v>2886600</v>
+        <v>2371200</v>
       </c>
       <c r="J66" s="3">
-        <v>2012600</v>
+        <v>2029600</v>
       </c>
       <c r="K66" s="3">
         <v>1552900</v>
@@ -3637,16 +3637,16 @@
         <v>83300</v>
       </c>
       <c r="F81" s="3">
-        <v>744500</v>
+        <v>750700</v>
       </c>
       <c r="G81" s="3">
-        <v>70300</v>
+        <v>80100</v>
       </c>
       <c r="H81" s="3">
-        <v>104400</v>
+        <v>117300</v>
       </c>
       <c r="I81" s="3">
-        <v>101600</v>
+        <v>106700</v>
       </c>
       <c r="J81" s="3">
         <v>144500</v>
@@ -3695,25 +3695,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>166200</v>
+        <v>25300</v>
       </c>
       <c r="E83" s="3">
-        <v>165800</v>
+        <v>18100</v>
       </c>
       <c r="F83" s="3">
-        <v>121700</v>
+        <v>-1800</v>
       </c>
       <c r="G83" s="3">
-        <v>141200</v>
+        <v>29400</v>
       </c>
       <c r="H83" s="3">
-        <v>131100</v>
+        <v>29100</v>
       </c>
       <c r="I83" s="3">
-        <v>97700</v>
+        <v>9600</v>
       </c>
       <c r="J83" s="3">
-        <v>95800</v>
+        <v>10100</v>
       </c>
       <c r="K83" s="3">
         <v>72200</v>
@@ -4228,25 +4228,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-20900</v>
+        <v>20900</v>
       </c>
       <c r="E96" s="3">
-        <v>-17900</v>
+        <v>17900</v>
       </c>
       <c r="F96" s="3">
-        <v>-7600</v>
+        <v>7600</v>
       </c>
       <c r="G96" s="3">
-        <v>-23200</v>
+        <v>23200</v>
       </c>
       <c r="H96" s="3">
-        <v>-69200</v>
+        <v>69200</v>
       </c>
       <c r="I96" s="3">
-        <v>-41800</v>
+        <v>41800</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>101700</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4452,26 +4452,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/NMRK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NMRK_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
   <si>
     <t>NMRK</t>
   </si>
@@ -656,61 +656,61 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -720,42 +720,45 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2738500</v>
+      </c>
+      <c r="E8" s="3">
         <v>2470400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2705500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2906400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1905000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2218100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2047600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1596500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1350000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1200200</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -765,9 +768,12 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -792,15 +798,15 @@
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="3">
         <v>18000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18500</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -810,42 +816,45 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2738500</v>
+      </c>
+      <c r="E10" s="3">
         <v>2470400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2705500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2906400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1905000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2218100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2047600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1596500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1332000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1181800</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -855,9 +864,12 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,35 +887,36 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>2900</v>
+        <v>7900</v>
       </c>
       <c r="E12" s="3">
-        <v>2100</v>
+        <v>7100</v>
       </c>
       <c r="F12" s="3">
-        <v>1300</v>
+        <v>5400</v>
       </c>
       <c r="G12" s="3">
         <v>1300</v>
       </c>
       <c r="H12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I12" s="3">
         <v>2000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>400</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -919,9 +932,12 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,36 +980,39 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E14" s="3">
         <v>20400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>128100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1227900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-25700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-69700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-123700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-68000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1009,42 +1028,45 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>171000</v>
+      </c>
+      <c r="E15" s="3">
         <v>163000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>151800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>121700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>135200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>126100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>97700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>89500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>73100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>72000</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1054,9 +1076,12 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,41 +1096,42 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2576000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2338900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2394700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2879700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1735100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2048800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1841500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1466200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1182600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1211500</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1115,42 +1141,45 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>162500</v>
+      </c>
+      <c r="E18" s="3">
         <v>131400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>310800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>26700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>169900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>169300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>206100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>130200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>167400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-11200</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1160,9 +1189,12 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,41 +1212,42 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>-14200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2800</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3">
         <v>11900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-6600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>41900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1900</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1224,39 +1257,42 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>333500</v>
+      </c>
+      <c r="E21" s="3">
         <v>308700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>465500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>148400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>293200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>302100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>262000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>221300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>243400</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1269,36 +1305,39 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E22" s="3">
         <v>38300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>33700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>35300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>40300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>36600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>700</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -1314,42 +1353,45 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>131300</v>
+      </c>
+      <c r="E23" s="3">
         <v>103500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>154600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1221100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>146300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>214100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>282400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>202600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>171200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9400</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1359,42 +1401,45 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E24" s="3">
         <v>41100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>42100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>243000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>37000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>52400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>90500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>57500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-6600</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1404,9 +1449,12 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,42 +1497,45 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>85500</v>
+      </c>
+      <c r="E26" s="3">
         <v>62400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>112500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>978100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>109300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>161700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>191900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>145100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>167200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2700</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1494,42 +1545,45 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>61200</v>
+      </c>
+      <c r="E27" s="3">
         <v>42600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>83300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>744500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>70300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>104400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>101600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>144500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>168400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2800</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,9 +1593,12 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1611,8 +1671,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>3</v>
@@ -1629,9 +1689,12 @@
       <c r="P29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,42 +1785,45 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>14200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2800</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3">
         <v>-11900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>6600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-41900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1900</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1764,42 +1833,45 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>61200</v>
+      </c>
+      <c r="E33" s="3">
         <v>42600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>83300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>750700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>80100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>117300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>106700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>144500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>168400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2800</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1809,9 +1881,12 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,42 +1929,45 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>61200</v>
+      </c>
+      <c r="E35" s="3">
         <v>42600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>83300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>750700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>80100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>117300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>106700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>144500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>168400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2800</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1899,47 +1977,50 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1949,9 +2030,12 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,41 +2073,42 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>197700</v>
+      </c>
+      <c r="E41" s="3">
         <v>164900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>233000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>191300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>191400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>163600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>122500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>121000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>66600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>111400</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2032,36 +2118,39 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>524600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>33300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>36800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>48900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>57600</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2077,42 +2166,45 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>607900</v>
+      </c>
+      <c r="E43" s="3">
         <v>632100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>545700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>594900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>386000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>530900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>482100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>210500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1331800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>643600</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2122,9 +2214,12 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2149,8 +2244,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2167,42 +2262,45 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>34900</v>
+        <v>33500</v>
       </c>
       <c r="E45" s="3">
+        <v>35000</v>
+      </c>
+      <c r="F45" s="3">
         <v>37800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>29500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>35700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>53500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>32200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>84300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>71900</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2212,42 +2310,45 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1772700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1506100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1076000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2524400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1819100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1073500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1757100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>825100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1482700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>826900</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2257,42 +2358,45 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E47" s="3">
         <v>4900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>100000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>108300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>111000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>194100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>154700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>107600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>187100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>94300</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2302,42 +2406,45 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>667200</v>
+      </c>
+      <c r="E48" s="3">
         <v>774400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>794200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>742400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>286800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>299700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>78800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>64800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>56500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>25800</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2347,42 +2454,45 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1352900</v>
+      </c>
+      <c r="E49" s="3">
         <v>1391400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1355400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1283600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1099400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1016800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>962900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>895100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>783000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>684000</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2392,9 +2502,12 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,42 +2598,45 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>43800</v>
+      </c>
+      <c r="E52" s="3">
         <v>43400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>19600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>34000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>24400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>31000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>65200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>25500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>26800</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2527,9 +2646,12 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,42 +2694,45 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4710100</v>
+      </c>
+      <c r="E54" s="3">
         <v>4471600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3940800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5216200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3982500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3201600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3454200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2273000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2534700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1657900</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2617,9 +2742,12 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,41 +2785,42 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>272300</v>
+      </c>
+      <c r="E57" s="3">
         <v>266500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>208200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>223200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>97300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>162000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>113700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>79400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>57500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>48700</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2700,42 +2830,45 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>862700</v>
+      </c>
+      <c r="E58" s="3">
         <v>605700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>782100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1272700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1123900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>273600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>972400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>418100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>258000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>359600</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2745,42 +2878,45 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E59" s="3">
         <v>39800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>42100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>80700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>90000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>146100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>112500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>50400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1094900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>317700</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2790,42 +2926,45 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1780400</v>
+      </c>
+      <c r="E60" s="3">
         <v>1489600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1576100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2192700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1705300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1045400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1664600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>782600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1410400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>726000</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2835,42 +2974,45 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1160500</v>
+      </c>
+      <c r="E61" s="3">
         <v>1145300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>627100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1131300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>899000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>817200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>537900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1083200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>300</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -2880,42 +3022,45 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>224800</v>
+      </c>
+      <c r="E62" s="3">
         <v>235400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>191200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>207000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>437000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>376800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>168600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>163800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>140100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>127600</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2925,9 +3070,12 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,42 +3214,45 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3172100</v>
+      </c>
+      <c r="E66" s="3">
         <v>2876600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2399300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3531100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3041300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2239500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2371200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2029600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1552900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>857700</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3105,9 +3262,12 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3259,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,36 +3474,39 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1207300</v>
+      </c>
+      <c r="E72" s="3">
         <v>1166700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1145000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1079700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>342800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>313100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>278000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>199500</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,9 +3522,12 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,42 +3666,45 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1205500</v>
+      </c>
+      <c r="E76" s="3">
         <v>1252900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1181300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1277900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>655000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>599700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>567600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>260400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>981800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>800200</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3529,9 +3714,12 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,47 +3762,50 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3624,42 +3815,45 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>61200</v>
+      </c>
+      <c r="E81" s="3">
         <v>42600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>83300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>750700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>80100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>117300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>106700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>144500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>168400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2800</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3669,9 +3863,12 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,8 +3886,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3698,29 +3896,29 @@
         <v>25300</v>
       </c>
       <c r="E83" s="3">
-        <v>18100</v>
+        <v>21100</v>
       </c>
       <c r="F83" s="3">
+        <v>14800</v>
+      </c>
+      <c r="G83" s="3">
         <v>-1800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>29400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>29100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>10100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>72200</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3733,9 +3931,12 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,39 +4171,42 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-266000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1196300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-48700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-777700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>986800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-332400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>853600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-644200</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4003,9 +4219,12 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,38 +4242,39 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-31500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-55400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-62200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-19700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-19600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-34500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-21000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-19100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-27300</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4067,9 +4287,12 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,39 +4383,42 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-33400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-49700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>308600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>453100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-56800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>7700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-34400</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4202,9 +4431,12 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,35 +4454,36 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E96" s="3">
         <v>20900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>17900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>7600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>23200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>69200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>41800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>101700</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -4266,9 +4499,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,39 +4643,42 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>89500</v>
+      </c>
+      <c r="E100" s="3">
         <v>261500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1458500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-396300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>817800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-895500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>338700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-798200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>636000</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4446,9 +4691,12 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4473,14 +4721,14 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4491,39 +4739,42 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>46200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-54200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>46500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>8100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>36500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>34500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>14000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>55800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-42600</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4536,7 +4787,10 @@
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/NMRK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NMRK_YR_FIN.xlsx
@@ -1315,10 +1315,10 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>51000</v>
+        <v>52000</v>
       </c>
       <c r="E22" s="3">
-        <v>38300</v>
+        <v>42800</v>
       </c>
       <c r="F22" s="3">
         <v>33700</v>

--- a/AAII_Financials/Yearly/NMRK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NMRK_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="92">
   <si>
     <t>NMRK</t>
   </si>
@@ -656,64 +656,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
@@ -723,45 +723,48 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3294000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2738500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2470400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2705500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2906400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1905000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2218100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2047600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1596500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1350000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1200200</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
@@ -771,9 +774,12 @@
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -801,15 +807,15 @@
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3">
         <v>18000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18500</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
@@ -819,45 +825,48 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>3294000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2738500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2470400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2705500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2906400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1905000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2218100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2047600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1596500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1332000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1181800</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
@@ -867,9 +876,12 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -888,38 +900,39 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E12" s="3">
         <v>7900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5400</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1300</v>
       </c>
       <c r="H12" s="3">
         <v>1300</v>
       </c>
       <c r="I12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J12" s="3">
         <v>2000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>400</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -935,9 +948,12 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,39 +999,42 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-600</v>
+        <v>-33000</v>
       </c>
       <c r="E14" s="3">
-        <v>20400</v>
+        <v>-500</v>
       </c>
       <c r="F14" s="3">
+        <v>19800</v>
+      </c>
+      <c r="G14" s="3">
         <v>128100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1227900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-25700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-69700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-123700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-68000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1031,45 +1050,48 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>174100</v>
+      </c>
+      <c r="E15" s="3">
         <v>171000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>163000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>151800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>121700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>135200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>126100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>97700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>89500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>73100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>72000</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1079,9 +1101,12 @@
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1097,44 +1122,45 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3093000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2576000</v>
       </c>
-      <c r="E17" s="3">
-        <v>2338900</v>
-      </c>
       <c r="F17" s="3">
+        <v>2339600</v>
+      </c>
+      <c r="G17" s="3">
         <v>2394700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2879700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1735100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2048800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1841500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1466200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1182600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1211500</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1144,45 +1170,48 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>201000</v>
+      </c>
+      <c r="E18" s="3">
         <v>162500</v>
       </c>
-      <c r="E18" s="3">
-        <v>131400</v>
-      </c>
       <c r="F18" s="3">
+        <v>130800</v>
+      </c>
+      <c r="G18" s="3">
         <v>310800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>26700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>169900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>169300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>206100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>130200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>167400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-11200</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1192,9 +1221,12 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1213,44 +1245,45 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
         <v>-14200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2800</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3">
         <v>11900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-6600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>41900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1900</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1260,42 +1293,45 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>375100</v>
+      </c>
+      <c r="E21" s="3">
         <v>333500</v>
       </c>
-      <c r="E21" s="3">
-        <v>308700</v>
-      </c>
       <c r="F21" s="3">
+        <v>308000</v>
+      </c>
+      <c r="G21" s="3">
         <v>465500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>148400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>293200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>302100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>262000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>221300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>243400</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1308,39 +1344,42 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>56200</v>
+      </c>
+      <c r="E22" s="3">
         <v>52000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>42800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>33700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>35300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>40300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>36600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>700</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -1356,45 +1395,48 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>201500</v>
+      </c>
+      <c r="E23" s="3">
         <v>131300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>103500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>154600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1221100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>146300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>214100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>282400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>202600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>171200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9400</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1404,45 +1446,48 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>46100</v>
+      </c>
+      <c r="E24" s="3">
         <v>45800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>41100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>42100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>243000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>37000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>52400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>90500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>57500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-6600</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1452,9 +1497,12 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1500,45 +1548,48 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>155400</v>
+      </c>
+      <c r="E26" s="3">
         <v>85500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>62400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>112500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>978100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>109300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>161700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>191900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>145100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>167200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2700</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1548,45 +1599,48 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>126200</v>
+      </c>
+      <c r="E27" s="3">
         <v>61200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>42600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>83300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>744500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>70300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>104400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>101600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>144500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>168400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2800</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1596,9 +1650,12 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1644,9 +1701,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1674,8 +1734,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>3</v>
@@ -1692,9 +1752,12 @@
       <c r="Q29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1740,9 +1803,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1788,45 +1854,48 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
         <v>14200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2800</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3">
         <v>-11900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>6600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-41900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1900</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1836,45 +1905,48 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>126200</v>
+      </c>
+      <c r="E33" s="3">
         <v>61200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>42600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>83300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>750700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>80100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>117300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>106700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>144500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>168400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2800</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1884,9 +1956,12 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1932,45 +2007,48 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>126200</v>
+      </c>
+      <c r="E35" s="3">
         <v>61200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>42600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>83300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>750700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>80100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>117300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>106700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>144500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>168400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2800</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1980,50 +2058,53 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2033,9 +2114,12 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2054,8 +2138,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2074,44 +2159,45 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>229100</v>
+      </c>
+      <c r="E41" s="3">
         <v>197700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>164900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>233000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>191300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>191400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>163600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>122500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>121000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>66600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>111400</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2121,9 +2207,12 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2134,26 +2223,26 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>524600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>33300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>36800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>48900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>57600</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2169,45 +2258,48 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>607900</v>
+        <v>628400</v>
       </c>
       <c r="E43" s="3">
+        <v>604900</v>
+      </c>
+      <c r="F43" s="3">
         <v>632100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>545700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>594900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>386000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>530900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>482100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>210500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1331800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>643600</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2217,9 +2309,12 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2247,8 +2342,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2265,45 +2360,48 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>33500</v>
+        <v>154900</v>
       </c>
       <c r="E45" s="3">
+        <v>36500</v>
+      </c>
+      <c r="F45" s="3">
         <v>35000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>37800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>29500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>35700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>53500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>32200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>84300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>71900</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2313,45 +2411,48 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2005000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1772700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1506100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1076000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2524400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1819100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1073500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1757100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>825100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1482700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>826900</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2361,45 +2462,48 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E47" s="3">
         <v>5200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>100000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>108300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>111000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>194100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>154700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>107600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>187100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>94300</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2409,45 +2513,48 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>604300</v>
+      </c>
+      <c r="E48" s="3">
         <v>667200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>774400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>794200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>742400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>286800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>299700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>78800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>64800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>56500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>25800</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2457,45 +2564,48 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1396400</v>
+      </c>
+      <c r="E49" s="3">
         <v>1352900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1391400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1355400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1283600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1099400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1016800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>962900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>895100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>783000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>684000</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2505,9 +2615,12 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2553,9 +2666,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2601,45 +2717,48 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E52" s="3">
         <v>43800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>43400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>19600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>34000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>24400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>31000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>65200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>25500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>26800</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2649,9 +2768,12 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2697,45 +2819,48 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5019200</v>
+      </c>
+      <c r="E54" s="3">
         <v>4710100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4471600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3940800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5216200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3982500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3201600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3454200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2273000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2534700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1657900</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2745,9 +2870,12 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2766,8 +2894,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2786,44 +2915,45 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>259400</v>
+      </c>
+      <c r="E57" s="3">
         <v>272300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>266500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>208200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>223200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>97300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>162000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>113700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>79400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>57500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>48700</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2833,45 +2963,48 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>993800</v>
+      </c>
+      <c r="E58" s="3">
         <v>862700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>605700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>782100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1272700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1123900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>273600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>972400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>418100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>258000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>359600</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2881,45 +3014,48 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E59" s="3">
         <v>6000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>39800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>42100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>80700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>90000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>146100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>112500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>50400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1094900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>317700</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2929,45 +3065,48 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1906900</v>
+      </c>
+      <c r="E60" s="3">
         <v>1780400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1489600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1576100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2192700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1705300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1045400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1664600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>782600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1410400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>726000</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2977,45 +3116,48 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1109000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1160500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1145300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>627100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1131300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>899000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>817200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>537900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1083200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>300</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3025,45 +3167,48 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>245200</v>
+      </c>
+      <c r="E62" s="3">
         <v>224800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>235400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>191200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>207000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>437000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>376800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>168600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>163800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>140100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>127600</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3073,9 +3218,12 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3121,9 +3269,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3169,9 +3320,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3217,45 +3371,48 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3267400</v>
+      </c>
+      <c r="E66" s="3">
         <v>3172100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2876600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2399300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3531100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3041300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2239500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2371200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2029600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1552900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>857700</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3265,9 +3422,12 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3286,8 +3446,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3333,9 +3494,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3381,9 +3545,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3429,9 +3596,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3477,39 +3647,42 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1311700</v>
+      </c>
+      <c r="E72" s="3">
         <v>1207300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1166700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1145000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1079700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>342800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>313100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>278000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>199500</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3525,9 +3698,12 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3573,9 +3749,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3621,9 +3800,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3669,45 +3851,48 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1461600</v>
+      </c>
+      <c r="E76" s="3">
         <v>1205500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1252900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1181300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1277900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>655000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>599700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>567600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>260400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>981800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>800200</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3717,9 +3902,12 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3765,50 +3953,53 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3818,45 +4009,48 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>126200</v>
+      </c>
+      <c r="E81" s="3">
         <v>61200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>42600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>83300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>750700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>80100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>117300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>106700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>144500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>168400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2800</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,9 +4060,12 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3887,41 +4084,42 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E83" s="3">
         <v>25300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>21100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>14800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>-1800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>29400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>29100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>9600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>10100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>72200</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3934,9 +4132,12 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3982,9 +4183,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4030,9 +4234,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4078,9 +4285,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4126,9 +4336,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4174,42 +4387,45 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>172000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-9900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-266000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1196300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-48700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-777700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>986800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-332400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>853600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-644200</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4222,9 +4438,12 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4243,41 +4462,42 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-29400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-31500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-55400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-62200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-19700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-19600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-34500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-21000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-19100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-27300</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4290,9 +4510,12 @@
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4338,9 +4561,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4386,42 +4612,45 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-198100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-33400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-49700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>308600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>453100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-56800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>7700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-34400</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4434,9 +4663,12 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4455,38 +4687,39 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E96" s="3">
         <v>20600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>20900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>17900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>7600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>23200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>69200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>41800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>101700</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -4502,9 +4735,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4550,9 +4786,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4598,9 +4837,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4646,42 +4888,45 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-44800</v>
+      </c>
+      <c r="E100" s="3">
         <v>89500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>261500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1458500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-396300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>817800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-895500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>338700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-798200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>636000</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4694,9 +4939,12 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4724,14 +4972,14 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -4742,42 +4990,45 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="E102" s="3">
         <v>46200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-54200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>46500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>8100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>36500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>34500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>14000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>55800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-42600</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,7 +5041,10 @@
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
